--- a/custom/Maptivity_Cards.xlsx
+++ b/custom/Maptivity_Cards.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ncesmart.sharepoint.com/sites/ResearchandInnovation/Delte dokumenter/4-Social_Innovation/Social Innovation DATABASE/PROJECTS/EU PROJECTS/8. PROBONO/WP8/T8.2/Events/ENLIT 2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="8_{DC3DB2FC-8228-4A1B-8150-BE6D11335097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B046D1CC-01AB-42CB-982A-8A2F30FA1BDC}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="8_{DC3DB2FC-8228-4A1B-8150-BE6D11335097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D53C6A10-209C-4962-A6A8-DBE9CBCDD707}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{DB883E9A-5E53-4B3C-8244-DC114755194E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{DB883E9A-5E53-4B3C-8244-DC114755194E}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="3" r:id="rId1"/>
     <sheet name="ENLIT TOTAL" sheetId="6" state="hidden" r:id="rId2"/>
     <sheet name="SHIRE" sheetId="7" r:id="rId3"/>
     <sheet name="GOTHAM CITY" sheetId="8" r:id="rId4"/>
-    <sheet name="HOGSMEADE" sheetId="10" r:id="rId5"/>
+    <sheet name="CORUSCANT" sheetId="9" r:id="rId5"/>
+    <sheet name="HOGSMEADE" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="51">
   <si>
     <t>This document aims at collecting information to create cards for the Placemaking Maptivity - see examples from Dublin workshop on first tab</t>
   </si>
@@ -206,7 +207,8 @@
 Visitors can see the results on a small screen showing energy savings and comfort levels. “It’s a simple change, but it makes a big difference for visitors and staff,” says the museum coordinator. </t>
   </si>
   <si>
-    <t>The local energy community is piloting a digital twin interface integrated with an interoperability platform. Residents can visualize and simulate their building’s flexibility behavior in real time. This digital layer helps users better understand how smart devices, solar panels, EV chargers, and battery storage systems interact—and how they can monetize their flexibility.  Unlike traditional dashboards, this twin translates device activity into actionable flexibility scenarios, guiding households to earn revenue by shifting demand at the right time. Early results show improved engagement and a 22% increase in automated flexibility events.</t>
+    <t xml:space="preserve">The city has built a brand new, innovative “green museum.”  With new insulation, solar windows and an upgraded ventilation system, it keeps a steady indoor climate using much less energy.
+Visitors can see the results on a small screen showing energy savings and comfort levels. “It’s a simple change, but it makes a big difference for visitors and staff,” says the museum coordinator. </t>
   </si>
 </sst>
 </file>
@@ -266,7 +268,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -282,24 +284,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -332,7 +316,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -350,46 +334,25 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1014,13 +977,13 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="13.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="9"/>
-    <col min="2" max="2" width="23.54296875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="88.7265625" style="9" customWidth="1"/>
-    <col min="4" max="16384" width="13.54296875" style="9"/>
+    <col min="1" max="1" width="13.54296875" style="13"/>
+    <col min="2" max="2" width="23.54296875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="88.7265625" style="13" customWidth="1"/>
+    <col min="4" max="16384" width="13.54296875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -1035,80 +998,113 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:3" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="14" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C5" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="s">
+    <row r="6" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B6" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C6" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="116" x14ac:dyDescent="0.35">
-      <c r="A6" s="10" t="s">
+    <row r="7" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+      <c r="A7" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
+    <row r="8" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C8" s="9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="87" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
+    <row r="9" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B10" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>50</v>
+      <c r="C10" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1122,13 +1118,13 @@
   <sheetPr>
     <tabColor theme="2" tint="-0.89999084444715716"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="13.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="9"/>
-    <col min="2" max="2" width="23.54296875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="88.7265625" style="9" customWidth="1"/>
-    <col min="4" max="16384" width="13.54296875" style="9"/>
+    <col min="1" max="1" width="13.54296875" style="13"/>
+    <col min="2" max="2" width="23.54296875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="88.7265625" style="13" customWidth="1"/>
+    <col min="4" max="16384" width="13.54296875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -1143,79 +1139,112 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>14</v>
+      <c r="B2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="15" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C8" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="17" t="s">
+    <row r="9" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C11" s="9" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1225,11 +1254,150 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8075EAD4-CB57-437D-BB77-E726B08EDFFE}">
+  <sheetPr>
+    <tabColor rgb="FFC00000"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" customWidth="1"/>
+    <col min="2" max="2" width="17.90625" customWidth="1"/>
+    <col min="3" max="3" width="95.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="208" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="96" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="145" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7634C775-B33D-4370-B95B-DF8217F6D125}">
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.08984375" customWidth="1"/>
@@ -1248,106 +1416,121 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
+    <row r="3" spans="1:3" ht="139" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C5" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+    <row r="6" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C6" s="9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="116" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+    <row r="7" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C7" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="20" t="s">
+    <row r="8" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C8" s="9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="20" t="s">
+    <row r="9" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B9" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C9" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="20" t="s">
+    <row r="10" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C11" s="9" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dfe0bc08-805b-464b-a3b3-14f481cc2590">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="e03720ea-dd5e-4a49-a4bd-e892daaf4b36" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <e29f718226244c5d9254df24bafbec68 xmlns="dfe0bc08-805b-464b-a3b3-14f481cc2590">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </e29f718226244c5d9254df24bafbec68>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Interview1 xmlns="dfe0bc08-805b-464b-a3b3-14f481cc2590">true</Interview1>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006E13A86247895D46BF435FDF51976F2D" ma:contentTypeVersion="24" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="a2a402dcdd1f80a7438787bde6980b68">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="dfe0bc08-805b-464b-a3b3-14f481cc2590" xmlns:ns3="e03720ea-dd5e-4a49-a4bd-e892daaf4b36" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8dc986e030ac0f26afbe6f8e84c59588" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1639,6 +1822,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dfe0bc08-805b-464b-a3b3-14f481cc2590">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="e03720ea-dd5e-4a49-a4bd-e892daaf4b36" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <e29f718226244c5d9254df24bafbec68 xmlns="dfe0bc08-805b-464b-a3b3-14f481cc2590">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </e29f718226244c5d9254df24bafbec68>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Interview1 xmlns="dfe0bc08-805b-464b-a3b3-14f481cc2590">true</Interview1>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1649,18 +1849,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6421568-FE48-4CEF-8E7D-62C8D16CCC78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dfe0bc08-805b-464b-a3b3-14f481cc2590"/>
-    <ds:schemaRef ds:uri="e03720ea-dd5e-4a49-a4bd-e892daaf4b36"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E3F855F-82A8-4A0A-B52C-A66015B9F0AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1680,6 +1868,18 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6421568-FE48-4CEF-8E7D-62C8D16CCC78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dfe0bc08-805b-464b-a3b3-14f481cc2590"/>
+    <ds:schemaRef ds:uri="e03720ea-dd5e-4a49-a4bd-e892daaf4b36"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD1197B6-9771-41C3-99C2-6E9891938990}">
   <ds:schemaRefs>
